--- a/pre-processing/data_cleaned/camera.xlsx
+++ b/pre-processing/data_cleaned/camera.xlsx
@@ -1070,7 +1070,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1124,7 +1124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1149,6 +1149,9 @@
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1459,7 +1462,7 @@
     <col min="2" max="2" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -4471,7 +4474,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="3">
         <v>99350407</v>
       </c>
@@ -4509,7 +4512,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3">
         <v>41319582</v>
       </c>
@@ -4547,7 +4550,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3">
         <v>277965399</v>
       </c>
@@ -4585,7 +4588,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3">
         <v>277827500</v>
       </c>
@@ -4623,7 +4626,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3">
         <v>277534704</v>
       </c>
@@ -4661,7 +4664,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="3">
         <v>277470272</v>
       </c>
@@ -4699,7 +4702,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3">
         <v>277381589</v>
       </c>
@@ -4737,7 +4740,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3">
         <v>277356246</v>
       </c>
@@ -4775,7 +4778,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="3">
         <v>275815779</v>
       </c>
@@ -4813,7 +4816,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3">
         <v>275773160</v>
       </c>
@@ -4851,7 +4854,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3">
         <v>275511061</v>
       </c>
@@ -4889,7 +4892,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3">
         <v>275326681</v>
       </c>
@@ -4927,7 +4930,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3">
         <v>274847176</v>
       </c>
@@ -4965,7 +4968,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3">
         <v>274179036</v>
       </c>
@@ -5003,7 +5006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3">
         <v>273474185</v>
       </c>
@@ -5041,7 +5044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="3">
         <v>273446601</v>
       </c>
@@ -5079,7 +5082,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="3">
         <v>273026293</v>
       </c>
@@ -5117,7 +5120,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="3">
         <v>272178556</v>
       </c>
@@ -5155,7 +5158,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="3">
         <v>271705499</v>
       </c>
@@ -5193,7 +5196,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="3">
         <v>271248861</v>
       </c>
@@ -5231,7 +5234,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="3">
         <v>270906792</v>
       </c>
@@ -5269,7 +5272,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="3">
         <v>263987622</v>
       </c>

--- a/pre-processing/data_cleaned/camera.xlsx
+++ b/pre-processing/data_cleaned/camera.xlsx
@@ -34,82 +34,196 @@
     <t>Đồng hồ đo Áp suất lốp Ô tô</t>
   </si>
   <si>
+    <t>Camera wifi Yoosee Ngoài Trời 20MPX 4 Mắt 3 Màn Hình Kép Q10-28 Phiên Bản Mới 2025,Đêm Có Màu, Đàm Thoại Hai Chiều, Chống Nước Nhựa IP66, Hàng Nhập Khẩu</t>
+  </si>
+  <si>
+    <t>Camera Yoosee Wifi Ngoài Trời 2 Mắt Xem Cùng Lúc, Góc rộng, Đàm Thoại, IP66 Chống Nước, Báo Động, Hàng Nhập Khẩu - Bảo Hành 12 Tháng</t>
+  </si>
+  <si>
+    <t>Pin Dành Cho Máy Ảnh Nikon EN-EL14 1500mAh Cao Cấp - Hàng Nhập Khẩu</t>
+  </si>
+  <si>
+    <t>Thẻ Vietmap Live Pro Chính Hãng 2025, cảnh báo tốc độ, camera phạt nguội dùng trên điện thoại, Android.box, Màn hình Ô Tô - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera hành trình 70mai M310 Ghi hình 2K (QHD) Góc quay rộng 130° (Cam trước) - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera IP Wifi EZVIZ C6N Pro 2K (3MP) - Phiên bản nâng cấp của C6N - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera wifi Ezviz ngoài trời H8C PRO 3MP phát hiện chuyển động, quay 360, đàm thoại 2 chiều- Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Bộ dây đeo ngực 5 chi tiết cho máy quay hành động, smartphone 077, hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera Wifi Ngoài trời TP-Link Tapo C520WS - Độ phân giải 2K 4MP, Chống chịu thời tiết IP66, Có màu ban đêm - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera wifi trong nhà TP-Link Tapo C220 - Độ phân giải 4K 2MP, Đàm thoại 2 chiều, Quay quét 360 độ - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>Camera IP Wifi Trong Nhà EZVIZ C6N 1080p - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera IP Trong nhà Tapo C212 - Quay quét 360, Độ phân giải 2K 3MP, Đàm thoại 2 chiều, Có hồng ngoại ban đêm - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>Camera Wifi Ezviz 2 Mắt Trong Nhà H7C 2K 8MP, quay 360 độ, có màu ban đêm, đàm thoại 2 chiều - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera Wifi Ezviz 2 Mắt Ngoài Trời H9C 3K 6MP/10MP, quay 360 độ, đàm thoại 2 chiều - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera WiFi TP-Link Tapo C510W / C520WS An Ninh Quay/Quét 360 Độ, Chống Nước - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera Wifi EZVIZ H3C 2MP Có Màu Ban Đêm, H3C 1080P Mic thu âm - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>(Mẫu 2024) Camera 4G Yoosee 2 MẮT XEM 2 MÀN HÌNH 5.0MPX xoay 360 độ, xem đêm có màu, hỗ trợ đàm thoại 2 chiều - hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera Yoosee Wifi 2 Mắt Ngoài Trời 2 Màn Hình 5MP Xem Đêm Có Màu, Hỗ Trợ Đàm Thoại 2 Chiều Xoay 360 Độ - Hàng Nhập Khẩu</t>
+  </si>
+  <si>
+    <t>Camera WiFi Yoosee 2 Mắt Ngoài Trời, Xem 2 Màn Hình Cùng Lúc, Giám Sát Ngoài Trời Chống Nước IP66 - Hàng nhập Khẩu</t>
+  </si>
+  <si>
+    <t>CAMERA Yoosee 2 MẮT TRONG NHÀ 4MP KẾT NỐI WIFI, XOAY 360 ĐỘ, ĐÀM THOẠI 2 CHIỀU - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera wifi trong nhà quay quét 3MP IMOU IPC-A32EP-L - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera WiFi TP-Link Tapo C510W An Ninh Quay/Quét 360 Độ, Chống Nước - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera Wifi Yoosee 2 Mắt Xem 2 Màn Hình Cùng Lúc Ngoài Trời - Hàng Nhập Khẩu</t>
+  </si>
+  <si>
+    <t>CAMERA WIFI IMOU A22EP 1080P XOAY 360 ĐỘ - ĐÀM THOẠI 2 CHIỀU - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>Camera IMOU Cue 2, Camera Wifi độ phân giải 2 megapixel, đàm thoại 2 chiều, phát hiện người bằng AI thông minh - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Kính lọc Kingma Pro MC ND1000 (giảm 10 Stop), Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera WiFi Ngoài Trời TP-Link Tapo C320WS Độ Phân Giải 2K QHD - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera IP WIFI IMOU RANGER A2 Full HD 1080P, phiên bản 2022 - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Thẻ nhớ 32/64/128/256gb MIXIE  MicroSD  Class10 U3. Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>bộ chuyển nguồn poe 48v-12v dùng cho camera, Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Đầu đọc thẻ nhớ SSK cho máy ảnh - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera IP Wifi Trong Nhà Ezviz Mini CS-C1C-B 1080p - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera IP Wifi TP-Link Tapo C200 Full HD 1080P Giám sát An Ninh - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Pin Panasonic CR 1632 -Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera wifi yoosee 3.0  2K siêu nét - camera ip yoosee 3 râu 3mp trong nhà - hàng nhập khẩu</t>
+  </si>
+  <si>
+    <t>Pin chính hãng Kingma - Sony NP-FW50 - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Gói hút ẩm đa dụng loại 2gr - 100g - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Pin Máy Ảnh Nikon EN-EL3e - Hàng Nhập Khẩu</t>
+  </si>
+  <si>
+    <t>Chân Máy Ảnh Tripod Weifeng 6662A - Hàng Nhập Khẩu</t>
+  </si>
+  <si>
     <t>Bộ chuyển đổi nguồn điện 220V sang 12V cổng ra tẩu điện trên ô tô</t>
   </si>
   <si>
-    <t>Camera wifi Yoosee Ngoài Trời 20MPX 4 Mắt 3 Màn Hình Kép Q10-28 Phiên Bản Mới 2025,Đêm Có Màu, Đàm Thoại Hai Chiều, Chống Nước Nhựa IP66, Hàng Nhập Khẩu</t>
-  </si>
-  <si>
-    <t>Camera Yoosee Wifi Ngoài Trời 2 Mắt Xem Cùng Lúc, Góc rộng, Đàm Thoại, IP66 Chống Nước, Báo Động, Hàng Nhập Khẩu - Bảo Hành 12 Tháng</t>
-  </si>
-  <si>
-    <t>Pin Dành Cho Máy Ảnh Nikon EN-EL14 1500mAh Cao Cấp - Hàng Nhập Khẩu</t>
-  </si>
-  <si>
-    <t>Thẻ Vietmap Live Pro Chính Hãng 2025, cảnh báo tốc độ, camera phạt nguội dùng trên điện thoại, Android.box, Màn hình Ô Tô - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera hành trình 70mai M310 Ghi hình 2K (QHD) Góc quay rộng 130° (Cam trước) - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera IP Wifi EZVIZ C6N Pro 2K (3MP) - Phiên bản nâng cấp của C6N - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera wifi Ezviz ngoài trời H8C PRO 3MP phát hiện chuyển động, quay 360, đàm thoại 2 chiều- Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Bộ dây đeo ngực 5 chi tiết cho máy quay hành động, smartphone 077, hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera Wifi Ngoài trời TP-Link Tapo C520WS - Độ phân giải 2K 4MP, Chống chịu thời tiết IP66, Có màu ban đêm - Hàng chính hãng</t>
+    <t>Balo máy ảnh, balo camera chống nước NATOLI, nhiều ngăn đựng laptop đi du lịch Chính hãng BST Durable Premium Camera Backpack B29</t>
+  </si>
+  <si>
+    <t>Chân Đế Camera, Giá Đỡ Camera Dán Tường Trong Suốt - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Nguồn Adapter 12V 2A; 3A; 5A; 6A Cho Đèn Led, Camera - Hàng Chính Hãng - 12V2A 24W</t>
   </si>
   <si>
     <t>Thẻ nhớ 32GB/ 64GB SDHC/ SDXC Lexar 800X PRO UHS-I BLUE Series, tốc độ đọc lên đến 150Mb/s - HÀNG CHÍNH HÃNG</t>
   </si>
   <si>
-    <t>Camera IP Wifi Trong Nhà EZVIZ C6N 1080p - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera IP Trong nhà Tapo C212 - Quay quét 360, Độ phân giải 2K 3MP, Đàm thoại 2 chiều, Có hồng ngoại ban đêm - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Camera Wifi Ezviz 2 Mắt Trong Nhà H7C 2K 8MP, quay 360 độ, có màu ban đêm, đàm thoại 2 chiều - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera Wifi Ezviz 2 Mắt Ngoài Trời H9C 3K 6MP/10MP, quay 360 độ, đàm thoại 2 chiều - Hàng chính hãng</t>
+    <t>1 kg gói hút ẩm 5/10/20gr nhãn hiệu MAXDESI hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera IP WiFi Quay Quét Ngoài Trời EZVIZ H8c 4MP 2K+ - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Godox SL100D / SL100Bi - Đèn Led Hỗ Trợ Cho Quay Phim, Chụp Hình, Điều Khiển APP, Công Suất Tối Đa 100W - Hàng chính hãng</t>
   </si>
   <si>
     <t>(MẪU MỚI) CAMERA YOOSEE BÓNG ĐÈN 2 MẮT QS211 FHD XEM 2 KHUNG HÌNH, HÌNH ẢNH SẮC NÉT, QUAY ĐÊM CÓ MÀU - HÀNG CHÍNH HÃNG</t>
   </si>
   <si>
-    <t>Camera WiFi TP-Link Tapo C510W / C520WS An Ninh Quay/Quét 360 Độ, Chống Nước - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera Wifi EZVIZ H3C 2MP Có Màu Ban Đêm, H3C 1080P Mic thu âm - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>(Mẫu 2024) Camera 4G Yoosee 2 MẮT XEM 2 MÀN HÌNH 5.0MPX xoay 360 độ, xem đêm có màu, hỗ trợ đàm thoại 2 chiều - hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera Yoosee Wifi 2 Mắt Ngoài Trời 2 Màn Hình 5MP Xem Đêm Có Màu, Hỗ Trợ Đàm Thoại 2 Chiều Xoay 360 Độ - Hàng Nhập Khẩu</t>
-  </si>
-  <si>
-    <t>Camera WiFi Yoosee 2 Mắt Ngoài Trời, Xem 2 Màn Hình Cùng Lúc, Giám Sát Ngoài Trời Chống Nước IP66 - Hàng nhập Khẩu</t>
-  </si>
-  <si>
-    <t>CAMERA Yoosee 2 MẮT TRONG NHÀ 4MP KẾT NỐI WIFI, XOAY 360 ĐỘ, ĐÀM THOẠI 2 CHIỀU - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera wifi trong nhà quay quét 3MP IMOU IPC-A32EP-L - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera WiFi TP-Link Tapo C510W An Ninh Quay/Quét 360 Độ, Chống Nước - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera Wifi Yoosee 2 Mắt Xem 2 Màn Hình Cùng Lúc Ngoài Trời - Hàng Nhập Khẩu</t>
-  </si>
-  <si>
-    <t>CAMERA WIFI IMOU A22EP 1080P XOAY 360 ĐỘ - ĐÀM THOẠI 2 CHIỀU - HÀNG CHÍNH HÃNG</t>
+    <t>Camera Wifi IMOU 2 Mắt Ngoài Trời S7XP Cruiser Dual 6MP/10MP, quay 360 độ, đàm thoại 2 chiều - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>[[MẪU NÂNG CẤP] Camera Wi-fi EZVIZ H1C/C1HC Trong Nhà, FHD 1080P, Góc Rộng Cố Định, Đàm Thoại Hai Chiều, Nén Video H265 - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera Wifi Ezviz CS-H1C (2.0MP) - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera Yoosee WiFi 2 Mắt Ngoài Trời QPT36 Xem 2 Màn Hình Cùng Lúc 5.0Mpx Giám Sát Ngoài Trời Chống Nước IP66 - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera IP Yoosee PTZ Ngoài Trời 2 Màn Hình 5MPX Xem Đêm Có Màu, Hỗ Trợ Đàm Thoại 2 Chiều Xoay 360 Độ - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera Yoosee WiFi 2 Mắt Siêu Nét - Xem 2 Màn Hình Cùng Lúc - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Flycam ZLL SG108 Max tích hợp cảm biến laser tránh vật cản thông minh - Thiết bị bay có sóng wifi 5G thế hệ mới - Hàng nhập khẩu</t>
+  </si>
+  <si>
+    <t>Hohem Isteady XE / XE Kit - Gimbal Chống Rung Cho Smartphone, Tải Trọng 280g, Sử Dụng 8 Giờ- Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera IP WIFI IMOU RANGER 2 IPC - A22EP Full HD 1080P - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera Yoosee PT năng lượng mặt trời CG19-46 (Solar PT Camera 4.0MPx) - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>1 Kg gói hút ẩm loại 10gr (100 gói) nhãn hiệu MAX DESI hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera IP Wifi trong nhà EZVIZ C6N 4M 2K, xoay 360 độ ezviz C6N Full HD, đàm thoại 2 chiều - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera IMOU Cruiser 2MP/4MP, Camera ngoài trời, xoay 360, chống nước, tích hợp đèn chiếu sáng, có màu ban đêm - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera IP Wifi Ngoài Trời EZVIZ H3 5MP Độ Phân Giải 3K Siêu Nét Tích Hợp AI Nhận Diện Vẫy Tay Chào - Có Màu Ban Đêm - Đàm Thoại 2 Chiều - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera IP Wifi Ngoài Trời EZVIZ C3TN 3MP 2K Color Night Vision Tích Hợp Ai - Có Màu Ban Đêm - Đàm Thoại 2 Chiều - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera Wifi Trong Nhà EZVIZ C6N 2M FHD 1080P Quay 355 độ - Đàm thoại 2 chiều - Hàng Chính Hãng</t>
   </si>
   <si>
     <t>Camera IP Wifi quay quét thông minh EZVIZ C6N 2.0 4.0MP - Hàng Chính Hãng</t>
@@ -118,595 +232,595 @@
     <t>Camera Có Màu Ban Đêm IP hồng ngoại không dây 2.0 3.0 Megapixel EZVIZ C3TN  - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Camera IMOU Cue 2, Camera Wifi độ phân giải 2 megapixel, đàm thoại 2 chiều, phát hiện người bằng AI thông minh - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera WiFi Ngoài Trời TP-Link Tapo C320WS Độ Phân Giải 2K QHD - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera IP WIFI IMOU RANGER A2 Full HD 1080P, phiên bản 2022 - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Thẻ nhớ 32/64/128/256gb MIXIE  MicroSD  Class10 U3. Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>bộ chuyển nguồn poe 48v-12v dùng cho camera, Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Đầu đọc thẻ nhớ SSK cho máy ảnh - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Pin Panasonic CR 1632 -Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera wifi yoosee 3.0  2K siêu nét - camera ip yoosee 3 râu 3mp trong nhà - hàng nhập khẩu</t>
-  </si>
-  <si>
-    <t>Camera Wi-Fi TP-Link Tapo C200 1080P (2MP) An Ninh Gia Đình Có Thể Điều Chỉnh Hướng - Hàng Chính Hãng</t>
+    <t>Camera WiFi Ngoài Trời TP-Link Tapo C320WS 4MP - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera Imou Range 2C - New 2021 - Chip Hình Ảnh Thế Hệ Mới - Wifi Cực Mạnh Siêu Khỏe - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera IP 360 độ 1080P TP-Link Tapo C200 Trắng - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Combo Camera Wi-fi Trong Nhà EZVIZ C1C-B 2MP Kèm Thẻ Nhớ  32GB/64G - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Tripod - Chân đế điện thoại, chân đế máy ảnh Yunteng VCT 5208 kiêm giá đỡ có remote Bluetooth điều khiển chụp từ xa</t>
+  </si>
+  <si>
+    <t>Combo pin sạc Kingma cho Nikon EN-EL14, Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera Wifi Trong Nhà Yoosee 3.0 Full HD, 3 Râu, Xoay 360 độ , Đàm Thoại 2 Chiều, Cảm Biến Báo Động – Hàng nhập khẩu</t>
+  </si>
+  <si>
+    <t>Camera IP WiFi EZVIZ CS - C1C - 2MP</t>
+  </si>
+  <si>
+    <t>Camera Wifi TP-Link Tapo C310 3MP An Ninh Ngoài Trời - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>2 Pin + 1 Đốc sạc đôi Sony NP-FW50 - Chính hãng KingMa</t>
   </si>
   <si>
     <t>Gói hút ẩm Secco - Hàng chính hãng</t>
   </si>
   <si>
-    <t>Gói hút ẩm đa dụng loại 2gr - 100g - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Balo máy ảnh, balo camera chống nước NATOLI, nhiều ngăn đựng laptop đi du lịch Chính hãng BST Durable Premium Camera Backpack B29</t>
-  </si>
-  <si>
-    <t>Camera hành trình VIETMAP TS-C9P - Hàng chính hãng</t>
+    <t>Chân Máy Ảnh Tripod Weifeng 3520 - Hàng Nhập Khẩu</t>
+  </si>
+  <si>
+    <t>Máy Chụp Ảnh Mini Kèm Thẻ 512G T Retro Kỹ Thuật Số CCD 4K Cho Học Sinh – Nhỏ Gọn, Thời Trang, Chụp Siêu Nét- HÀNG CHÍNH HÃNG MINIIN</t>
+  </si>
+  <si>
+    <t>Bộ Nắp van báo áp suất lốp Ô tô, Xe máy</t>
+  </si>
+  <si>
+    <t>Camera hành trình ô tô độ phân giải 2K, Wifi, UHD thương hiệu HP F965S - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Ulanzi MT-79 / MT-89 - Tripod Đa Năng Cho Máy Ảnh, Điện Thoại, Thiết Bị Chiếu Sáng, Chiều Cao Đa Dạng - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera WiFi quay quét EZVIZ H6C Pro 3K 5MP - hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Camera Nội Soi Công Nghiệp Chống Nước Kết Nối Điện Thoại AN112 - Hàng Nhập Khẩu</t>
   </si>
   <si>
     <t>Camera quan sát Xiaomi C400 Smart 2.5K - Hàng Nhập Khẩu</t>
   </si>
   <si>
-    <t>Chân Đế Camera, Giá Đỡ Camera Dán Tường Trong Suốt - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Nguồn Adapter 12V 2A; 3A; 5A; 6A Cho Đèn Led, Camera - Hàng Chính Hãng - 12V2A 24W</t>
-  </si>
-  <si>
-    <t>Thẻ nhớ SD Sandisk Ultra GN3 32GB 100MB/s UHS-I (cho máy ảnh) - Hàng Chính Hãng</t>
+    <t>Camera trong nhà TP-Link Tapo TC60 - Full HD, Đàm thoại 2 chiều, Phát hiện chuyển động - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>Camera hành trình SJCAM C110 Plus bản 2024 - Actioncam C110+ 4K Wifi chống rung kép camera mini - Hàng nhập khẩu</t>
+  </si>
+  <si>
+    <t>Camera IP 360 Độ 2MP TP-Link Tapo TC70 - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Máy Dò Camera Ẩn XM SMOOVIE Chống Quay Lén và Cảnh Báo Chống Trộm - Thiết Bị Dò Hồng Ngoại Phát Hiện Chuyển Động - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>ROGTZ - Camera nội soi P10 Chống nước IP68 Màn hình IPS 2.8 inch Đường kính camera 3.9mm Độ phân giải cao 1080p 8 đèn LED Đa ngôn ngữ  Pin lithium dung lượng cao 3.7V 2600mAh Nhà xưởng Y tế Cầm tay Ô tô Nhà cửa Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera Ngoài Trời NetCAM STD34, Quay Quét 360 độ, có Ống Kính Kép với Độ phân giải Siêu Nét 6MP - Hàng Chính Hãng</t>
   </si>
   <si>
     <t>Camera Năng Lượng Mặt Trời 4G Không Dây NetCAM STL4G, Chất lượng video HD 4MP, Dùng Sim 4G, Dung lượng pin 8000mAh - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>1 kg gói hút ẩm 5/10/20gr nhãn hiệu MAXDESI hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera IP WiFi Quay Quét Ngoài Trời EZVIZ H8c 4MP 2K+ - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Godox SL100D / SL100Bi - Đèn Led Hỗ Trợ Cho Quay Phim, Chụp Hình, Điều Khiển APP, Công Suất Tối Đa 100W - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera Wifi IMOU 2 Mắt Ngoài Trời S7XP Cruiser Dual 6MP/10MP, quay 360 độ, đàm thoại 2 chiều - Hàng chính hãng</t>
+    <t>Camera IP WiFi Yoosee R3 Có 3 Mắt Ngoài Trời Xem 3 Màn Hình Cùng Lúc, Độ Phân Giải 8.0Mpx - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Camera Hành Trình Ô Tô 3 Mắt S10 Plus Có WiFi Full HD 1080p Hỗ Trợ Kết Nối Điện Thoại Xem Qua App - Hàng Chính Hãng</t>
   </si>
   <si>
     <t>Camera Wifi TP-Link Tapo C211 Độ Phân Giải 2K UHD Quay Quét 360 Độ - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>[[MẪU NÂNG CẤP] Camera Wi-fi EZVIZ H1C/C1HC Trong Nhà, FHD 1080P, Góc Rộng Cố Định, Đàm Thoại Hai Chiều, Nén Video H265 - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera Wifi Ezviz CS-H1C (2.0MP) - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera Yoosee WiFi 2 Mắt Ngoài Trời QPT36 Xem 2 Màn Hình Cùng Lúc 5.0Mpx Giám Sát Ngoài Trời Chống Nước IP66 - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera IP Yoosee PTZ Ngoài Trời 2 Màn Hình 5MPX Xem Đêm Có Màu, Hỗ Trợ Đàm Thoại 2 Chiều Xoay 360 Độ - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera Yoosee WiFi 2 Mắt Siêu Nét - Xem 2 Màn Hình Cùng Lúc - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Flycam ZLL SG108 Max tích hợp cảm biến laser tránh vật cản thông minh - Thiết bị bay có sóng wifi 5G thế hệ mới - Hàng nhập khẩu</t>
-  </si>
-  <si>
-    <t>Camera Giám Sát Chống Trộm, Camera Wifi Mini Không Dây A9, Độ Phân Giải 720P, App Xem Từ Xa - HÀNG CHÍNH HÃNG MINIIN</t>
-  </si>
-  <si>
-    <t>Hohem Isteady XE / XE Kit - Gimbal Chống Rung Cho Smartphone, Tải Trọng 280g, Sử Dụng 8 Giờ- Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera IP WIFI IMOU RANGER 2 IPC - A22EP Full HD 1080P - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera Yoosee PT năng lượng mặt trời CG19-46 (Solar PT Camera 4.0MPx) - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera WiFi EZVIZ H8 3K - Độ Phân Giải 5MP, Bao Phủ Toàn Cảnh 360 Độ, Phát Hiện Con Người, Đàm Thoại 2 Chiều - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>1 Kg gói hút ẩm loại 10gr (100 gói) nhãn hiệu MAX DESI hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera IP Wifi trong nhà EZVIZ C6N 4M 2K, xoay 360 độ ezviz C6N Full HD, đàm thoại 2 chiều - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera IP WiFi Ngoài Trời EZVIZ H8 3K 5MP - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera IMOU Cruiser 2MP/4MP, Camera ngoài trời, xoay 360, chống nước, tích hợp đèn chiếu sáng, có màu ban đêm - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera IP Wifi Ngoài Trời EZVIZ H3 5MP Độ Phân Giải 3K Siêu Nét Tích Hợp AI Nhận Diện Vẫy Tay Chào - Có Màu Ban Đêm - Đàm Thoại 2 Chiều - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera IP Wifi Ngoài Trời EZVIZ C3TN 3MP 2K Color Night Vision Tích Hợp Ai - Có Màu Ban Đêm - Đàm Thoại 2 Chiều - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera Wifi Trong Nhà EZVIZ C6N 2M FHD 1080P Quay 355 độ - Đàm thoại 2 chiều - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera WiFi Ngoài Trời TP-Link Tapo C320WS 4MP - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Thẻ nhớ SDHC Sandisk Ultra 16GB upto 80MB/s UHS-I (cho máy ảnh) - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera IP wifi trong nhà IMOU Ranger 2 2MP/4MP - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera Imou Range 2C - New 2021 - Chip Hình Ảnh Thế Hệ Mới - Wifi Cực Mạnh Siêu Khỏe - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera IP 360 độ 1080P TP-Link Tapo C200 Trắng - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Combo Camera Wi-fi Trong Nhà EZVIZ C1C-B 2MP Kèm Thẻ Nhớ  32GB/64G - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Tripod - Chân đế điện thoại, chân đế máy ảnh Yunteng VCT 5208 kiêm giá đỡ có remote Bluetooth điều khiển chụp từ xa</t>
-  </si>
-  <si>
-    <t>Camera Wifi Trong Nhà Yoosee 3.0 Full HD, 3 Râu, Xoay 360 độ , Đàm Thoại 2 Chiều, Cảm Biến Báo Động – Hàng nhập khẩu</t>
-  </si>
-  <si>
-    <t>Camera IP WiFi EZVIZ CS - C1C - 2MP</t>
-  </si>
-  <si>
-    <t>Máy Chụp Ảnh Mini Kèm Thẻ 512G T Retro Kỹ Thuật Số CCD 4K Cho Học Sinh – Nhỏ Gọn, Thời Trang, Chụp Siêu Nét- HÀNG CHÍNH HÃNG MINIIN</t>
-  </si>
-  <si>
-    <t>Bộ Nắp van báo áp suất lốp Ô tô, Xe máy</t>
-  </si>
-  <si>
-    <t>Camera hành trình ô tô độ phân giải 2K, Wifi, UHD thương hiệu HP F965S - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Ulanzi MT-79 / MT-89 - Tripod Đa Năng Cho Máy Ảnh, Điện Thoại, Thiết Bị Chiếu Sáng, Chiều Cao Đa Dạng - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera WiFi quay quét EZVIZ H6C Pro 3K 5MP - hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Camera Nội Soi Công Nghiệp Chống Nước Kết Nối Điện Thoại AN112 - Hàng Nhập Khẩu</t>
-  </si>
-  <si>
-    <t>Camera hành trình SJCAM C110 Plus bản 2024 - Actioncam C110+ 4K Wifi chống rung kép camera mini - Hàng nhập khẩu</t>
-  </si>
-  <si>
-    <t>Camera IP 360 Độ 2MP TP-Link Tapo TC70 - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Máy Dò Camera Ẩn XM SMOOVIE Chống Quay Lén và Cảnh Báo Chống Trộm - Thiết Bị Dò Hồng Ngoại Phát Hiện Chuyển Động - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>ROGTZ - Camera nội soi P10 Chống nước IP68 Màn hình IPS 2.8 inch Đường kính camera 3.9mm Độ phân giải cao 1080p 8 đèn LED Đa ngôn ngữ  Pin lithium dung lượng cao 3.7V 2600mAh Nhà xưởng Y tế Cầm tay Ô tô Nhà cửa Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera Ngoài Trời NetCAM STD34, Quay Quét 360 độ, có Ống Kính Kép với Độ phân giải Siêu Nét 6MP - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera IP WiFi Yoosee R3 Có 3 Mắt Ngoài Trời Xem 3 Màn Hình Cùng Lúc, Độ Phân Giải 8.0Mpx - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera Wifi Yoosee PTZ 2 Mắt Xoay 360 Độ - Đàm Thoại 2 Chiều - Báo Động Chống Trộm - Ban Đêm Có Màu - hàng nhập khẩu</t>
-  </si>
-  <si>
-    <t>Bộ Dung Dịch Dụng Cụ Vệ Sinh Kai.N Cleaning Sulution Dành Cho iPhone, iPad, Laptop, Ống Kính Máy Ảnh, Thiết Bị Khác - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Camera Hành Trình Ô Tô 3 Mắt S10 Plus Có WiFi Full HD 1080p Hỗ Trợ Kết Nối Điện Thoại Xem Qua App - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Camera wifi AI thông minh Ezviz H6 5MP 3K siêu nét, xoay 360 Độ, Đàm thoại 2 chiều - hàng chính hãng</t>
-  </si>
-  <si>
     <t>Camera Wifi TP-Link Tapo C212 Độ Phân Giải 2K QHD Quay/Quét 360 Độ Hỗ Trợ Cổng LAN - Hàng Chính Hãng</t>
   </si>
   <si>
     <t>Camera Yoosee 2 Mắt Q26D Phiên bản Phóng To 6X Cực Nét - Camera kép xem cùng lúc trên điện thoại, Đàm thoại 2 Chiều, Ban Đêm Có Màu - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Camera Wifi TP-Link Tapo C220 Độ Phân Giải 2K QHD Quay/Quét 360 Độ Giám Sát An Ninh - Hàng Chính Hãng</t>
-  </si>
-  <si>
     <t>Camera Wifi TP-Link Tapo C200 / C210 Smart IR Full HD 1080P - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>images/camera/product_277854019.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_277827436.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_277601288.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_277417151.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_277015260.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_276857147.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_276711006.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_276376478.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_275918344.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_275856061.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_275257961.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_274954348.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_274879959.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_274567496.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_274184765.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_274184675.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_273932705.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_272967613.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_272268455.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_272030250.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_270977170.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_270977143.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_270977103.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_263596152.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_262891821.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_262792654.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_203898270.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_193105103.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_193102256.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_186103396.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_174896487.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_154259057.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_135839773.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_113427448.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_104070115.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_64672917.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_57071523.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_47868431.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_14585382.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_10716498.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_277497107.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_276862124.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_276021394.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_275959921.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_275544310.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_274728425.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_274724794.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_274069561.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_274065704.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_273951675.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_273644429.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_272366633.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_271234773.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_270964237.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_270545009.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_269944956.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_263972675.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_253489396.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_252006029.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_248585546.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_247421211.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_242482796.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_229766303.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_222452404.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_212934661.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_205985292.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_202904152.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_194130039.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_194121937.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_194067352.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_187642259.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_187036472.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_142796515.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_133876927.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_131416196.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_129078637.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_114789403.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_106641569.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_99350407.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_41319582.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_277965399.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_277827500.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_277534704.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_277470272.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_277381589.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_277356246.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_275815779.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_275773160.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_275511061.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_275326681.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_274847176.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_274179036.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_273474185.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_273446601.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_273026293.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_272178556.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_271705499.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_271248861.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_270906792.jpg</t>
-  </si>
-  <si>
-    <t>images/camera/product_263987622.jpg</t>
+    <t>images/camera/277854019.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/277601288.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/277417151.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/277015260.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/276857147.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/276711006.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/276376478.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/275918344.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/275856061.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/275257961.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/275255482.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/274879959.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/274567496.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/274184765.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/274184675.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/272967613.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/272268455.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/272030250.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/270977170.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/270977143.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/270977103.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/263596152.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/262891821.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/262792654.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/203898270.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/186103396.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/180847849.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/174896487.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/154259057.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/135839773.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/113427448.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/104070115.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/84866683.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/74500335.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/64672917.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/57071523.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/15375941.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/10716498.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/4713289.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/4688899.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/277827436.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/277497107.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/275959921.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/275544310.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/274954348.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/274069561.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/274065704.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/273951675.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/273932705.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/273644429.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/271234773.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/270964237.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/270545009.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/269944956.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/263972675.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/253489396.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/248585546.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/247421211.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/242482796.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/222452404.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/212934661.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/202904152.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/194130039.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/194121937.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/194067352.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/193105103.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/193102256.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/187642259.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/133876927.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/131416196.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/129078637.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/114789403.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/108747706.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/106641569.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/99350407.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/85764360.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/41319582.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/25309442.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/14585382.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/4688897.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/277965399.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/277827500.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/277534704.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/277470272.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/277381589.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/277356246.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/276021394.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/275938579.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/275815779.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/275773160.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/275511061.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/275326681.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/274847176.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/274724794.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/274179036.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/273026293.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/272366633.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/271705499.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/271248861.jpg</t>
+  </si>
+  <si>
+    <t>images/camera/263987622.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/b6/87/4f/48c64a4d36cc363b9c4360ec2dedf43e.jpg</t>
   </si>
   <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/88/8e/26/6c9162081c18287781445564043b5384.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/3a/0e/d2/dd1c0c947e6b90565c90d989ad60eb9a.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/63/fc/bf/9b3ecf8f5d730619ef1952a2e7106d2f.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c0/54/e9/db0ae0e51529f3b6a74c1d25f962a3a9.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/97/82/98/0eb365bcdd8eaeeb3a02d19cffcfcb01.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a8/b0/99/9e91f31ccbd1b2648c3b5e16e9505235.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/17/bd/25/d3023125cf7aa222008fafa0faad233d.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/33/72/fc/c050451d5e787f40f242a4e0f5d86f88.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e6/e2/9e/9d97c7b2053c5ba264283ff7f77d9b0f.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/84/b5/78/bb4eb05c63915428b04569bb3856c6f5.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/47/0e/24/942d12bfd874a4245cc3504e322f7e33.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7b/79/61/03d167c91ed3837d0bbec697302a0e12.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ab/85/04/cd52772c3bdab4e6c5dc301d582226a4.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/84/c9/c9/dd7a6aeeb363afdf9c3a095de6723a4a.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/38/e1/fa/00ac48202ff2e9170bb7cb6f826b1200.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/fb/dd/c2/9aec67df213f00e945af251d45f530d3.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/bd/96/fe/16cf8eb8c14ba0020de5a2a1d18e60f4.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/26/8a/b7/d9d1ecb3b069163a6b880f14c8af1742.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/26/8a/b7/72d6004a87191447c0321fd91058812d.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/81/d9/83/1f63f4e03dca987221641e9fd2c3e3bf.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/24/e7/f4/5737385e52fe8e483acc30c428b42ab1.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/43/61/1b/495b001c7af429380c504eb35986528f.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/26/8a/b7/efff0ef132a842dba53c34d934846bee.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/34/65/c1/432dfdc31db8a2614bf9b61ea15275bb.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8c/e3/23/a59ff6a0b5ba12c3bd7f360ee9ae1441.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1a/d3/3d/17b9550611e6a18c83db5ed93b36b879.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b0/7e/fd/98f93694d82a0ab06345450c93689c4b.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/26/4a/84/522fc87b2d78c736a155a08d8117cd2d.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/be/e8/40/9fbfbce7c393a9a199e3382983bc6fb2.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8f/e3/2a/3c1a160c24042920403e227d87c34e99.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/83/ab/b6/c648c432d9b5fd9694d7bc370f09a092.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/9a/a2/49/de9c55d15d8a0f3ece48f289ec661455.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/5a/f9/87/c1833e01dd5df975370dfdac00c2dc77.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/87/46/3b/36ca0faace8ec3e1f0121b856d5433a8.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/bc/49/b5/00ed099bfbaf358f7623db7b9ac3c308.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e7/ec/14/c6fa1df5ffe3e9a983e7797225059168.jpeg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/be/08/a4/28c3cd23a97eb7168fdc924c670d85f3.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a8/1b/9d/eb80f361e2b5e2431c9074f9dbdc8488.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6b/d9/35/04844094915a7098d04828f7ff29ef62.jpg</t>
+  </si>
+  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/e3/a6/d8/d414580041941f9d74ef07704f09b408.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/88/8e/26/6c9162081c18287781445564043b5384.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/3a/0e/d2/dd1c0c947e6b90565c90d989ad60eb9a.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/63/fc/bf/9b3ecf8f5d730619ef1952a2e7106d2f.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c0/54/e9/db0ae0e51529f3b6a74c1d25f962a3a9.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/97/82/98/0eb365bcdd8eaeeb3a02d19cffcfcb01.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a8/b0/99/9e91f31ccbd1b2648c3b5e16e9505235.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/17/bd/25/d3023125cf7aa222008fafa0faad233d.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/33/72/fc/c050451d5e787f40f242a4e0f5d86f88.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e6/e2/9e/9d97c7b2053c5ba264283ff7f77d9b0f.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b4/bb/75/2dea34c9bfa3b24ff159e594511ff47d.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/f5/07/5f/36f3719f5aee2e1eb850183e196f68dd.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/61/4f/61/ef46e0c2cdcd379e1337f18ab6cdc055.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/ff/74/d3/6669474b13948da024965970063c1b69.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/47/0e/24/942d12bfd874a4245cc3504e322f7e33.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7b/79/61/03d167c91ed3837d0bbec697302a0e12.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ab/85/04/cd52772c3bdab4e6c5dc301d582226a4.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/84/c9/c9/dd7a6aeeb363afdf9c3a095de6723a4a.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b2/fd/e8/81eee504626e70995e58c5ff9b6cc54e.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/5d/11/98/09aabde51ebe45c3324b4c34360ce0af.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8c/82/e3/fd3a10ce1e775dd7568cde19c0828581.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/22/1c/79/e72ab18e41b7413c66b82010aa127680.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/38/e1/fa/00ac48202ff2e9170bb7cb6f826b1200.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/fb/dd/c2/9aec67df213f00e945af251d45f530d3.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/bd/96/fe/16cf8eb8c14ba0020de5a2a1d18e60f4.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/26/8a/b7/d9d1ecb3b069163a6b880f14c8af1742.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/26/8a/b7/72d6004a87191447c0321fd91058812d.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/81/d9/83/1f63f4e03dca987221641e9fd2c3e3bf.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/24/e7/f4/5737385e52fe8e483acc30c428b42ab1.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/43/61/1b/495b001c7af429380c504eb35986528f.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/26/8a/b7/efff0ef132a842dba53c34d934846bee.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/34/65/c1/432dfdc31db8a2614bf9b61ea15275bb.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/44/02/52/7d3b9959b5349f2beb350285096d380b.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/3c/58/a8/6ac07475d7d2bd47c79cc9af976e1037.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/86/77/3b/9f477f5b9dd7b31c2668704a9dcb4eb7.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/34/27/5e/e5fd003aabc07944ebc07b61c25cd5c5.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/26/8a/b7/20ea09d2d237273b5b53533e862faaf4.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/33/c5/d6/9b0aa0a929e391e9280456e0ac57056f.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/40/d4/b4/deb53c96d1e611cc79fac7b39b35c1c7.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/87/7d/16/3f2a5287bb5327cba90649d16b2bbd47.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/cc/1f/ca/80db1500b8cc5c66a2940fb7f73b999a.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a4/5f/0e/d41988afef0ce6008baa49f07b19ce16.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1f/82/7e/0cc46bcdfa5d1a3dcf4ac0689fa84fee.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/47/0e/24/ec637cf87bf0b74cb7afef9a1a4db4f5.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8a/48/aa/5d4f20ecf2e53b58b28cf1dc0500cede.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/93/31/d3/046aa2a20e38e3cf139c25778a3318e9.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1b/e7/e6/861d1bea433fb8cbe33e99358a4269fd.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/47/0e/24/a2e1099c581e42b16d25510d22192e6d.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/68/10/1f/dedea39300584eb7f29797c52cc66b6f.jpg</t>
@@ -715,217 +829,103 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/55/5b/70/dc09e77be297495c84e88a8cfa18fb21.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8c/e3/23/a59ff6a0b5ba12c3bd7f360ee9ae1441.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b0/7e/fd/98f93694d82a0ab06345450c93689c4b.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/26/4a/84/522fc87b2d78c736a155a08d8117cd2d.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/82/b9/d7/fbb26ada4d2e10e627bbd522586a2dc0.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8f/e3/2a/3c1a160c24042920403e227d87c34e99.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/83/ab/b6/c648c432d9b5fd9694d7bc370f09a092.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/87/46/3b/36ca0faace8ec3e1f0121b856d5433a8.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/bc/49/b5/00ed099bfbaf358f7623db7b9ac3c308.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/04/96/1b/f70ffa0847d541a9a770084f11b18efc.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/57/d6/78/812e8a55679eacc1c1da0223814494a9.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1e/45/ef/52e0a8a8551f67af434459bbace1d503.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/36/09/65/df34b246fcb18fffca5f3be7025124ec.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e0/eb/75/a99ebb50b7863e8c385a2f8bbd8fccc6.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/4e/f4/47/0e3001cae5ba094820ea92fa59175bfb.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/46/96/e6/03105301bbd5ed636d86e9dd73a8b399.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/bc/49/b5/9f2cc5822c9b0690e2c604d3bb9fc071.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/bf/22/f1/399c270bfbd5e150c71002d1aae287bc.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/9a/0e/1a/89984cb2e8fa34887f72a974238d0685.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d7/b6/76/c98c8096611674ee675f3d6d03ec05c8.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/37/cf/7a/bb87121753c909e4853e9e2143709720.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/e8/a8/b6/8a9c782a6f8945bf6f9eaa0bc5764592.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/be/08/a4/28c3cd23a97eb7168fdc924c670d85f3.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b4/bb/75/2dea34c9bfa3b24ff159e594511ff47d.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/cd/79/79/ecfc95102ac86ab75173abe505974bc7.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d0/0a/05/05d07a21385ea2ef0f6a7f0dd67552b4.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/67/15/9f/fa0324a7671d53d49f0b00dd3ff1e2f3.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e1/ca/46/1830c24293df45b0766c9d0003798d67.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/33/a5/a7/b9fa1a7dbd0d208092fc04ba2111aca6.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b3/72/d8/f0aa333455a693ee44a2d81dd1dd1322.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6b/07/e2/98d157ffd567c5dbb79d9232c957ca2e.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/9b/fa/7c/e024c17b52effc1955f56413bbddc2d1.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/91/9f/b8/b2424fa652f666eda83d5a148645329e.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/f5/07/5f/36f3719f5aee2e1eb850183e196f68dd.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/61/4f/61/ef46e0c2cdcd379e1337f18ab6cdc055.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/9c/98/36/2b8f07c1ca233d861c4e589b25ff5247.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/bc/f7/59/234d5c1b063dfd5ec93c18fe3789f9d0.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1f/2c/a4/544fd14f5b0da8d34eac48e0cf3af6ae.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/83/b9/01/afe4926ccb948c1021e4d6bf725a07a1.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/4a/88/d8/32e76c61214443bc2a1bce128a0f4075.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d6/d7/1c/742430ccfe1d0e3113d38dd7fb0cd44b.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/52/32/04/7dac33f95e51ae89f9f88181337fa87f.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/e1/c7/d9/ac74e958b4780c3de51d3a1c54ac327c.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b2/fd/e8/81eee504626e70995e58c5ff9b6cc54e.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/5d/11/98/09aabde51ebe45c3324b4c34360ce0af.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8c/82/e3/fd3a10ce1e775dd7568cde19c0828581.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/44/02/52/7d3b9959b5349f2beb350285096d380b.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c6/6e/08/358ecfb3a456ea83fabe958dd0539818.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/21/dd/06/810c1b49b44da03886128e96ff2e7e96.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/5f/f0/4d/24c240730c514b34917b20fcc40a07e3.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/3c/58/a8/6ac07475d7d2bd47c79cc9af976e1037.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/86/77/3b/9f477f5b9dd7b31c2668704a9dcb4eb7.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/34/27/5e/e5fd003aabc07944ebc07b61c25cd5c5.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/26/8a/b7/20ea09d2d237273b5b53533e862faaf4.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/33/c5/d6/9b0aa0a929e391e9280456e0ac57056f.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/40/d4/b4/deb53c96d1e611cc79fac7b39b35c1c7.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ce/5b/da/7712af0248221c8984edae13ec60d95b.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/87/7d/16/3f2a5287bb5327cba90649d16b2bbd47.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/cc/1f/ca/80db1500b8cc5c66a2940fb7f73b999a.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a4/5f/0e/d41988afef0ce6008baa49f07b19ce16.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/35/e4/74/f7e0b7796b144e3ddd69adb11e64f3b2.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1f/82/7e/0cc46bcdfa5d1a3dcf4ac0689fa84fee.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/47/0e/24/ec637cf87bf0b74cb7afef9a1a4db4f5.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e1/27/95/e21651e627186efb96d40ff1d517004c.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8a/48/aa/5d4f20ecf2e53b58b28cf1dc0500cede.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/93/31/d3/046aa2a20e38e3cf139c25778a3318e9.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1b/e7/e6/861d1bea433fb8cbe33e99358a4269fd.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/47/0e/24/a2e1099c581e42b16d25510d22192e6d.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/57/d6/78/812e8a55679eacc1c1da0223814494a9.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/af/87/b9/80847c279aa4503fbad1f2f0af44bfdc.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/26/4a/84/bf5e06a0eac3792b27edc1b64e776c9b.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1e/45/ef/52e0a8a8551f67af434459bbace1d503.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/36/09/65/df34b246fcb18fffca5f3be7025124ec.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e0/eb/75/a99ebb50b7863e8c385a2f8bbd8fccc6.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/4e/f4/47/0e3001cae5ba094820ea92fa59175bfb.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/bc/49/b5/9f2cc5822c9b0690e2c604d3bb9fc071.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/bf/22/f1/399c270bfbd5e150c71002d1aae287bc.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d7/b6/76/c98c8096611674ee675f3d6d03ec05c8.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/67/15/9f/fa0324a7671d53d49f0b00dd3ff1e2f3.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e1/ca/46/1830c24293df45b0766c9d0003798d67.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/33/a5/a7/b9fa1a7dbd0d208092fc04ba2111aca6.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b3/72/d8/f0aa333455a693ee44a2d81dd1dd1322.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6b/07/e2/98d157ffd567c5dbb79d9232c957ca2e.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/9b/fa/7c/e024c17b52effc1955f56413bbddc2d1.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1f/2c/a4/544fd14f5b0da8d34eac48e0cf3af6ae.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/83/b9/01/afe4926ccb948c1021e4d6bf725a07a1.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/4a/88/d8/32e76c61214443bc2a1bce128a0f4075.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d6/d7/1c/742430ccfe1d0e3113d38dd7fb0cd44b.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/52/32/04/7dac33f95e51ae89f9f88181337fa87f.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c6/6e/08/358ecfb3a456ea83fabe958dd0539818.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d2/5e/7e/3146ff5bb31829008fc6ca0834208d9c.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c5/0b/0b/e096c3f0c5051f015b25b168d8afbaea.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/21/dd/06/810c1b49b44da03886128e96ff2e7e96.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a2/be/00/d11ffdda4e333befcb4fc65fe03cd1c1.png</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/b8/10/9b/f8c1cbd37f2a6c255e604d8a2367991e.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/9c/5a/0f/de1d8feaf18c9d86dc37020a1d988c5b.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c5/1c/d7/18cbb0ab6202da51d81f1593cb0469c7.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/89/28/d3/5dddbd6b7bede5f2947f40de6fa949d2.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d1/67/07/568d9a7a34490629c353958397cbda29.png</t>
   </si>
   <si>
     <t>Máy Ảnh - Máy Quay Phim</t>
@@ -1338,7 +1338,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>277827436</v>
+        <v>277601288</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -1355,7 +1355,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>277601288</v>
+        <v>277417151</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -1372,7 +1372,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>277417151</v>
+        <v>277015260</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>277015260</v>
+        <v>276857147</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -1406,7 +1406,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>276857147</v>
+        <v>276711006</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>276711006</v>
+        <v>276376478</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -1440,7 +1440,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>276376478</v>
+        <v>275918344</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -1457,7 +1457,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>275918344</v>
+        <v>275856061</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -1474,7 +1474,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>275856061</v>
+        <v>275257961</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>275257961</v>
+        <v>275255482</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>274954348</v>
+        <v>274879959</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
@@ -1525,7 +1525,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>274879959</v>
+        <v>274567496</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>274567496</v>
+        <v>274184765</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
@@ -1559,7 +1559,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>274184765</v>
+        <v>274184675</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>274184675</v>
+        <v>272967613</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>273932705</v>
+        <v>272268455</v>
       </c>
       <c r="B18" t="s">
         <v>21</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>272967613</v>
+        <v>272030250</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
@@ -1627,7 +1627,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>272268455</v>
+        <v>270977170</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
@@ -1644,7 +1644,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>272030250</v>
+        <v>270977143</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>270977170</v>
+        <v>270977103</v>
       </c>
       <c r="B22" t="s">
         <v>25</v>
@@ -1678,7 +1678,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>270977143</v>
+        <v>263596152</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>270977103</v>
+        <v>262891821</v>
       </c>
       <c r="B24" t="s">
         <v>27</v>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>263596152</v>
+        <v>262792654</v>
       </c>
       <c r="B25" t="s">
         <v>28</v>
@@ -1729,7 +1729,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>262891821</v>
+        <v>203898270</v>
       </c>
       <c r="B26" t="s">
         <v>29</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>262792654</v>
+        <v>186103396</v>
       </c>
       <c r="B27" t="s">
         <v>30</v>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>203898270</v>
+        <v>180847849</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
@@ -1780,7 +1780,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>193105103</v>
+        <v>174896487</v>
       </c>
       <c r="B29" t="s">
         <v>32</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>193102256</v>
+        <v>154259057</v>
       </c>
       <c r="B30" t="s">
         <v>33</v>
@@ -1814,7 +1814,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>186103396</v>
+        <v>135839773</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
@@ -1831,7 +1831,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>174896487</v>
+        <v>113427448</v>
       </c>
       <c r="B32" t="s">
         <v>35</v>
@@ -1848,7 +1848,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>154259057</v>
+        <v>104070115</v>
       </c>
       <c r="B33" t="s">
         <v>36</v>
@@ -1865,7 +1865,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>135839773</v>
+        <v>84866683</v>
       </c>
       <c r="B34" t="s">
         <v>37</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>113427448</v>
+        <v>74500335</v>
       </c>
       <c r="B35" t="s">
         <v>38</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>104070115</v>
+        <v>64672917</v>
       </c>
       <c r="B36" t="s">
         <v>39</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>64672917</v>
+        <v>57071523</v>
       </c>
       <c r="B37" t="s">
         <v>40</v>
@@ -1933,7 +1933,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>57071523</v>
+        <v>15375941</v>
       </c>
       <c r="B38" t="s">
         <v>41</v>
@@ -1950,7 +1950,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>47868431</v>
+        <v>10716498</v>
       </c>
       <c r="B39" t="s">
         <v>42</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>14585382</v>
+        <v>4713289</v>
       </c>
       <c r="B40" t="s">
         <v>43</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>10716498</v>
+        <v>4688899</v>
       </c>
       <c r="B41" t="s">
         <v>44</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>277497107</v>
+        <v>277827436</v>
       </c>
       <c r="B42" t="s">
         <v>45</v>
@@ -2018,7 +2018,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>276862124</v>
+        <v>277497107</v>
       </c>
       <c r="B43" t="s">
         <v>46</v>
@@ -2035,7 +2035,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>276021394</v>
+        <v>275959921</v>
       </c>
       <c r="B44" t="s">
         <v>47</v>
@@ -2052,7 +2052,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>275959921</v>
+        <v>275544310</v>
       </c>
       <c r="B45" t="s">
         <v>48</v>
@@ -2069,7 +2069,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>275544310</v>
+        <v>274954348</v>
       </c>
       <c r="B46" t="s">
         <v>49</v>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>274728425</v>
+        <v>274069561</v>
       </c>
       <c r="B47" t="s">
         <v>50</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>274724794</v>
+        <v>274065704</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
@@ -2120,7 +2120,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>274069561</v>
+        <v>273951675</v>
       </c>
       <c r="B49" t="s">
         <v>52</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>274065704</v>
+        <v>273932705</v>
       </c>
       <c r="B50" t="s">
         <v>53</v>
@@ -2154,7 +2154,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>273951675</v>
+        <v>273644429</v>
       </c>
       <c r="B51" t="s">
         <v>54</v>
@@ -2171,7 +2171,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>273644429</v>
+        <v>271234773</v>
       </c>
       <c r="B52" t="s">
         <v>55</v>
@@ -2188,7 +2188,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>272366633</v>
+        <v>270964237</v>
       </c>
       <c r="B53" t="s">
         <v>56</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>271234773</v>
+        <v>270545009</v>
       </c>
       <c r="B54" t="s">
         <v>57</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>270964237</v>
+        <v>269944956</v>
       </c>
       <c r="B55" t="s">
         <v>58</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>270545009</v>
+        <v>263972675</v>
       </c>
       <c r="B56" t="s">
         <v>59</v>
@@ -2256,7 +2256,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>269944956</v>
+        <v>253489396</v>
       </c>
       <c r="B57" t="s">
         <v>60</v>
@@ -2273,7 +2273,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>263972675</v>
+        <v>248585546</v>
       </c>
       <c r="B58" t="s">
         <v>61</v>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>253489396</v>
+        <v>247421211</v>
       </c>
       <c r="B59" t="s">
         <v>62</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>252006029</v>
+        <v>242482796</v>
       </c>
       <c r="B60" t="s">
         <v>63</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>248585546</v>
+        <v>222452404</v>
       </c>
       <c r="B61" t="s">
         <v>64</v>
@@ -2341,7 +2341,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>247421211</v>
+        <v>212934661</v>
       </c>
       <c r="B62" t="s">
         <v>65</v>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>242482796</v>
+        <v>202904152</v>
       </c>
       <c r="B63" t="s">
         <v>66</v>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>229766303</v>
+        <v>194130039</v>
       </c>
       <c r="B64" t="s">
         <v>67</v>
@@ -2392,7 +2392,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>222452404</v>
+        <v>194121937</v>
       </c>
       <c r="B65" t="s">
         <v>68</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>212934661</v>
+        <v>194067352</v>
       </c>
       <c r="B66" t="s">
         <v>69</v>
@@ -2426,7 +2426,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>205985292</v>
+        <v>193105103</v>
       </c>
       <c r="B67" t="s">
         <v>70</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>202904152</v>
+        <v>193102256</v>
       </c>
       <c r="B68" t="s">
         <v>71</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>194130039</v>
+        <v>187642259</v>
       </c>
       <c r="B69" t="s">
         <v>72</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>194121937</v>
+        <v>133876927</v>
       </c>
       <c r="B70" t="s">
         <v>73</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>194067352</v>
+        <v>131416196</v>
       </c>
       <c r="B71" t="s">
         <v>74</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>187642259</v>
+        <v>129078637</v>
       </c>
       <c r="B72" t="s">
         <v>75</v>
@@ -2528,7 +2528,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>187036472</v>
+        <v>114789403</v>
       </c>
       <c r="B73" t="s">
         <v>76</v>
@@ -2545,7 +2545,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>142796515</v>
+        <v>108747706</v>
       </c>
       <c r="B74" t="s">
         <v>77</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>133876927</v>
+        <v>106641569</v>
       </c>
       <c r="B75" t="s">
         <v>78</v>
@@ -2579,7 +2579,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>131416196</v>
+        <v>99350407</v>
       </c>
       <c r="B76" t="s">
         <v>79</v>
@@ -2596,7 +2596,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>129078637</v>
+        <v>85764360</v>
       </c>
       <c r="B77" t="s">
         <v>80</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>114789403</v>
+        <v>41319582</v>
       </c>
       <c r="B78" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="C78" t="s">
         <v>180</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>106641569</v>
+        <v>25309442</v>
       </c>
       <c r="B79" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C79" t="s">
         <v>181</v>
@@ -2647,10 +2647,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>99350407</v>
+        <v>14585382</v>
       </c>
       <c r="B80" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C80" t="s">
         <v>182</v>
@@ -2664,10 +2664,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>41319582</v>
+        <v>4688897</v>
       </c>
       <c r="B81" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="C81" t="s">
         <v>183</v>
@@ -2783,7 +2783,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88">
-        <v>275815779</v>
+        <v>276021394</v>
       </c>
       <c r="B88" t="s">
         <v>90</v>
@@ -2800,7 +2800,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>275773160</v>
+        <v>275938579</v>
       </c>
       <c r="B89" t="s">
         <v>91</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>275511061</v>
+        <v>275815779</v>
       </c>
       <c r="B90" t="s">
         <v>92</v>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>275326681</v>
+        <v>275773160</v>
       </c>
       <c r="B91" t="s">
         <v>93</v>
@@ -2851,7 +2851,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>274847176</v>
+        <v>275511061</v>
       </c>
       <c r="B92" t="s">
         <v>94</v>
@@ -2868,7 +2868,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>274179036</v>
+        <v>275326681</v>
       </c>
       <c r="B93" t="s">
         <v>95</v>
@@ -2885,7 +2885,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>273474185</v>
+        <v>274847176</v>
       </c>
       <c r="B94" t="s">
         <v>96</v>
@@ -2902,7 +2902,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>273446601</v>
+        <v>274724794</v>
       </c>
       <c r="B95" t="s">
         <v>97</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>273026293</v>
+        <v>274179036</v>
       </c>
       <c r="B96" t="s">
         <v>98</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>272178556</v>
+        <v>273026293</v>
       </c>
       <c r="B97" t="s">
         <v>99</v>
@@ -2953,7 +2953,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>271705499</v>
+        <v>272366633</v>
       </c>
       <c r="B98" t="s">
         <v>100</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>271248861</v>
+        <v>271705499</v>
       </c>
       <c r="B99" t="s">
         <v>101</v>
@@ -2987,7 +2987,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>270906792</v>
+        <v>271248861</v>
       </c>
       <c r="B100" t="s">
         <v>102</v>
